--- a/data/exchange_rates/EUR_CZK.xlsx
+++ b/data/exchange_rates/EUR_CZK.xlsx
@@ -451,189 +451,187 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45658</v>
+        <v>36161</v>
       </c>
       <c r="C2" t="n">
-        <v>25.104</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.003730454797999889</v>
-      </c>
+        <v>36.02</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45292</v>
+        <v>36528</v>
       </c>
       <c r="C3" t="n">
-        <v>25.198</v>
+        <v>34.795</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02127832043124072</v>
+        <v>-0.034</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44928</v>
+        <v>36893</v>
       </c>
       <c r="C4" t="n">
-        <v>24.673</v>
+        <v>31.696</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02174093092595654</v>
+        <v>-0.0891</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>44564</v>
+        <v>37258</v>
       </c>
       <c r="C5" t="n">
-        <v>24.148</v>
+        <v>31.54</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02871852626498265</v>
+        <v>-0.0049</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>44197</v>
+        <v>37623</v>
       </c>
       <c r="C6" t="n">
-        <v>24.862</v>
+        <v>32.27</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.05121355518241499</v>
+        <v>0.0231</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>43831</v>
+        <v>37987</v>
       </c>
       <c r="C7" t="n">
-        <v>26.204</v>
+        <v>30.4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03076075839823775</v>
+        <v>-0.0579</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>43466</v>
+        <v>38355</v>
       </c>
       <c r="C8" t="n">
-        <v>25.422</v>
+        <v>29.07</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.01070163832353966</v>
+        <v>-0.0437</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>43101</v>
+        <v>38719</v>
       </c>
       <c r="C9" t="n">
-        <v>25.697</v>
+        <v>27.48</v>
       </c>
       <c r="D9" t="n">
-        <v>0.006659615309280297</v>
+        <v>-0.0547</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>42737</v>
+        <v>39083</v>
       </c>
       <c r="C10" t="n">
-        <v>25.527</v>
+        <v>26.497</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.05480060724997225</v>
+        <v>-0.0358</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>42370</v>
+        <v>39448</v>
       </c>
       <c r="C11" t="n">
-        <v>27.007</v>
+        <v>26.753</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0003333580265204956</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>42005</v>
+        <v>39814</v>
       </c>
       <c r="C12" t="n">
-        <v>26.998</v>
+        <v>26.318</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.02365109214523362</v>
+        <v>-0.0163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>41640</v>
+        <v>40179</v>
       </c>
       <c r="C13" t="n">
-        <v>27.652</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0117078881896678</v>
+        <v>-0.0501</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>41275</v>
+        <v>40546</v>
       </c>
       <c r="C14" t="n">
-        <v>27.332</v>
+        <v>25.545</v>
       </c>
       <c r="D14" t="n">
-        <v>0.09118492494410742</v>
+        <v>0.0218</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>40910</v>
@@ -642,188 +640,190 @@
         <v>25.048</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.01945586220395394</v>
+        <v>-0.0195</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>40546</v>
+        <v>41275</v>
       </c>
       <c r="C16" t="n">
-        <v>25.545</v>
+        <v>27.332</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02180000000000007</v>
+        <v>0.0912</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>40179</v>
+        <v>41640</v>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>27.652</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.05007979329736307</v>
+        <v>0.0117</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>39814</v>
+        <v>42005</v>
       </c>
       <c r="C18" t="n">
-        <v>26.318</v>
+        <v>26.998</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.01625985870743463</v>
+        <v>-0.0237</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>39448</v>
+        <v>42370</v>
       </c>
       <c r="C19" t="n">
-        <v>26.753</v>
+        <v>27.007</v>
       </c>
       <c r="D19" t="n">
-        <v>0.009661471109936983</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>39083</v>
+        <v>42737</v>
       </c>
       <c r="C20" t="n">
-        <v>26.497</v>
+        <v>25.527</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.03577147016011647</v>
+        <v>-0.0548</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>38719</v>
+        <v>43101</v>
       </c>
       <c r="C21" t="n">
-        <v>27.48</v>
+        <v>25.697</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.05469556243550051</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>38355</v>
+        <v>43466</v>
       </c>
       <c r="C22" t="n">
-        <v>29.07</v>
+        <v>25.422</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.04374999999999995</v>
+        <v>-0.0107</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>37987</v>
+        <v>43831</v>
       </c>
       <c r="C23" t="n">
-        <v>30.4</v>
+        <v>26.204</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05794855903315787</v>
+        <v>0.0308</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>37623</v>
+        <v>44197</v>
       </c>
       <c r="C24" t="n">
-        <v>32.27</v>
+        <v>24.862</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02314521242866214</v>
+        <v>-0.0512</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>37258</v>
+        <v>44564</v>
       </c>
       <c r="C25" t="n">
-        <v>31.54</v>
+        <v>24.148</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.004921756688541215</v>
+        <v>-0.0287</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>36893</v>
+        <v>44928</v>
       </c>
       <c r="C26" t="n">
-        <v>31.696</v>
+        <v>24.673</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.08906452076447766</v>
+        <v>0.0217</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>36528</v>
+        <v>45292</v>
       </c>
       <c r="C27" t="n">
-        <v>34.795</v>
+        <v>25.198</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.03400888395335928</v>
+        <v>0.0213</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>36161</v>
+        <v>45658</v>
       </c>
       <c r="C28" t="n">
-        <v>36.02</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+        <v>25.104</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.0037</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/exchange_rates/EUR_CZK.xlsx
+++ b/data/exchange_rates/EUR_CZK.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,6 +448,11 @@
           <t>Returns</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Z-Score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -460,6 +465,7 @@
         <v>36.02</v>
       </c>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -474,6 +480,9 @@
       <c r="D3" t="n">
         <v>-0.034</v>
       </c>
+      <c r="E3" t="n">
+        <v>-0.5620482880753954</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -488,6 +497,9 @@
       <c r="D4" t="n">
         <v>-0.0891</v>
       </c>
+      <c r="E4" t="n">
+        <v>-2.04353932302813</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -502,6 +514,9 @@
       <c r="D5" t="n">
         <v>-0.0049</v>
       </c>
+      <c r="E5" t="n">
+        <v>0.2203725670448331</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -516,6 +531,9 @@
       <c r="D6" t="n">
         <v>0.0231</v>
       </c>
+      <c r="E6" t="n">
+        <v>0.9732173760952246</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -530,6 +548,9 @@
       <c r="D7" t="n">
         <v>-0.0579</v>
       </c>
+      <c r="E7" t="n">
+        <v>-1.204655107229122</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -544,6 +565,9 @@
       <c r="D8" t="n">
         <v>-0.0437</v>
       </c>
+      <c r="E8" t="n">
+        <v>-0.8228552397821381</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -558,6 +582,9 @@
       <c r="D9" t="n">
         <v>-0.0547</v>
       </c>
+      <c r="E9" t="n">
+        <v>-1.118615700480506</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -572,6 +599,9 @@
       <c r="D10" t="n">
         <v>-0.0358</v>
       </c>
+      <c r="E10" t="n">
+        <v>-0.6104454543714919</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -586,6 +616,9 @@
       <c r="D11" t="n">
         <v>0.0097</v>
       </c>
+      <c r="E11" t="n">
+        <v>0.6129273603353944</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -600,6 +633,9 @@
       <c r="D12" t="n">
         <v>-0.0163</v>
       </c>
+      <c r="E12" t="n">
+        <v>-0.08614281949711203</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -614,6 +650,9 @@
       <c r="D13" t="n">
         <v>-0.0501</v>
       </c>
+      <c r="E13" t="n">
+        <v>-0.9949340532793705</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -628,6 +667,9 @@
       <c r="D14" t="n">
         <v>0.0218</v>
       </c>
+      <c r="E14" t="n">
+        <v>0.9382638671035993</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -642,6 +684,9 @@
       <c r="D15" t="n">
         <v>-0.0195</v>
       </c>
+      <c r="E15" t="n">
+        <v>-0.1721822262457282</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -656,6 +701,9 @@
       <c r="D16" t="n">
         <v>0.0912</v>
       </c>
+      <c r="E16" t="n">
+        <v>2.804243500964212</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -670,6 +718,9 @@
       <c r="D17" t="n">
         <v>0.0117</v>
       </c>
+      <c r="E17" t="n">
+        <v>0.6667019895532795</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -684,6 +735,9 @@
       <c r="D18" t="n">
         <v>-0.0237</v>
       </c>
+      <c r="E18" t="n">
+        <v>-0.2851089476032869</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -698,6 +752,9 @@
       <c r="D19" t="n">
         <v>0.0003</v>
       </c>
+      <c r="E19" t="n">
+        <v>0.3601866030113344</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -712,6 +769,9 @@
       <c r="D20" t="n">
         <v>-0.0548</v>
       </c>
+      <c r="E20" t="n">
+        <v>-1.121304431941401</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -726,6 +786,9 @@
       <c r="D21" t="n">
         <v>0.0067</v>
       </c>
+      <c r="E21" t="n">
+        <v>0.5322654165085667</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -740,6 +803,9 @@
       <c r="D22" t="n">
         <v>-0.0107</v>
       </c>
+      <c r="E22" t="n">
+        <v>0.06442614231296626</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -754,6 +820,9 @@
       <c r="D23" t="n">
         <v>0.0308</v>
       </c>
+      <c r="E23" t="n">
+        <v>1.180249698584082</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -768,6 +837,9 @@
       <c r="D24" t="n">
         <v>-0.0512</v>
       </c>
+      <c r="E24" t="n">
+        <v>-1.024510099349207</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -782,6 +854,9 @@
       <c r="D25" t="n">
         <v>-0.0287</v>
       </c>
+      <c r="E25" t="n">
+        <v>-0.4195455206479998</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -796,6 +871,9 @@
       <c r="D26" t="n">
         <v>0.0217</v>
       </c>
+      <c r="E26" t="n">
+        <v>0.9355751356427051</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -810,6 +888,9 @@
       <c r="D27" t="n">
         <v>0.0213</v>
       </c>
+      <c r="E27" t="n">
+        <v>0.924820209799128</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -823,6 +904,9 @@
       </c>
       <c r="D28" t="n">
         <v>-0.0037</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.2526373445755641</v>
       </c>
     </row>
   </sheetData>

--- a/data/exchange_rates/EUR_CZK.xlsx
+++ b/data/exchange_rates/EUR_CZK.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,10 +445,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Returns</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Z-Score</t>
         </is>
@@ -464,8 +469,11 @@
       <c r="C2" t="n">
         <v>36.02</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>1999</v>
+      </c>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -478,9 +486,12 @@
         <v>34.795</v>
       </c>
       <c r="D3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E3" t="n">
         <v>-0.034</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>-0.5620482880753954</v>
       </c>
     </row>
@@ -495,9 +506,12 @@
         <v>31.696</v>
       </c>
       <c r="D4" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E4" t="n">
         <v>-0.0891</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>-2.04353932302813</v>
       </c>
     </row>
@@ -512,9 +526,12 @@
         <v>31.54</v>
       </c>
       <c r="D5" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E5" t="n">
         <v>-0.0049</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.2203725670448331</v>
       </c>
     </row>
@@ -529,9 +546,12 @@
         <v>32.27</v>
       </c>
       <c r="D6" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.0231</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.9732173760952246</v>
       </c>
     </row>
@@ -546,9 +566,12 @@
         <v>30.4</v>
       </c>
       <c r="D7" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E7" t="n">
         <v>-0.0579</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>-1.204655107229122</v>
       </c>
     </row>
@@ -563,9 +586,12 @@
         <v>29.07</v>
       </c>
       <c r="D8" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E8" t="n">
         <v>-0.0437</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>-0.8228552397821381</v>
       </c>
     </row>
@@ -580,9 +606,12 @@
         <v>27.48</v>
       </c>
       <c r="D9" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E9" t="n">
         <v>-0.0547</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-1.118615700480506</v>
       </c>
     </row>
@@ -597,9 +626,12 @@
         <v>26.497</v>
       </c>
       <c r="D10" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E10" t="n">
         <v>-0.0358</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-0.6104454543714919</v>
       </c>
     </row>
@@ -614,9 +646,12 @@
         <v>26.753</v>
       </c>
       <c r="D11" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.0097</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.6129273603353944</v>
       </c>
     </row>
@@ -631,9 +666,12 @@
         <v>26.318</v>
       </c>
       <c r="D12" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E12" t="n">
         <v>-0.0163</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-0.08614281949711203</v>
       </c>
     </row>
@@ -648,9 +686,12 @@
         <v>25</v>
       </c>
       <c r="D13" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E13" t="n">
         <v>-0.0501</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>-0.9949340532793705</v>
       </c>
     </row>
@@ -665,9 +706,12 @@
         <v>25.545</v>
       </c>
       <c r="D14" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E14" t="n">
         <v>0.0218</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>0.9382638671035993</v>
       </c>
     </row>
@@ -682,9 +726,12 @@
         <v>25.048</v>
       </c>
       <c r="D15" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E15" t="n">
         <v>-0.0195</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>-0.1721822262457282</v>
       </c>
     </row>
@@ -699,9 +746,12 @@
         <v>27.332</v>
       </c>
       <c r="D16" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E16" t="n">
         <v>0.0912</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>2.804243500964212</v>
       </c>
     </row>
@@ -716,9 +766,12 @@
         <v>27.652</v>
       </c>
       <c r="D17" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E17" t="n">
         <v>0.0117</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>0.6667019895532795</v>
       </c>
     </row>
@@ -733,9 +786,12 @@
         <v>26.998</v>
       </c>
       <c r="D18" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E18" t="n">
         <v>-0.0237</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>-0.2851089476032869</v>
       </c>
     </row>
@@ -750,9 +806,12 @@
         <v>27.007</v>
       </c>
       <c r="D19" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.0003</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>0.3601866030113344</v>
       </c>
     </row>
@@ -767,9 +826,12 @@
         <v>25.527</v>
       </c>
       <c r="D20" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E20" t="n">
         <v>-0.0548</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>-1.121304431941401</v>
       </c>
     </row>
@@ -784,9 +846,12 @@
         <v>25.697</v>
       </c>
       <c r="D21" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.0067</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>0.5322654165085667</v>
       </c>
     </row>
@@ -801,9 +866,12 @@
         <v>25.422</v>
       </c>
       <c r="D22" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E22" t="n">
         <v>-0.0107</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>0.06442614231296626</v>
       </c>
     </row>
@@ -818,9 +886,12 @@
         <v>26.204</v>
       </c>
       <c r="D23" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E23" t="n">
         <v>0.0308</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>1.180249698584082</v>
       </c>
     </row>
@@ -835,9 +906,12 @@
         <v>24.862</v>
       </c>
       <c r="D24" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E24" t="n">
         <v>-0.0512</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>-1.024510099349207</v>
       </c>
     </row>
@@ -852,9 +926,12 @@
         <v>24.148</v>
       </c>
       <c r="D25" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E25" t="n">
         <v>-0.0287</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>-0.4195455206479998</v>
       </c>
     </row>
@@ -869,9 +946,12 @@
         <v>24.673</v>
       </c>
       <c r="D26" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E26" t="n">
         <v>0.0217</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>0.9355751356427051</v>
       </c>
     </row>
@@ -886,9 +966,12 @@
         <v>25.198</v>
       </c>
       <c r="D27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E27" t="n">
         <v>0.0213</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>0.924820209799128</v>
       </c>
     </row>
@@ -903,9 +986,12 @@
         <v>25.104</v>
       </c>
       <c r="D28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E28" t="n">
         <v>-0.0037</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>0.2526373445755641</v>
       </c>
     </row>

--- a/data/exchange_rates/EUR_CZK.xlsx
+++ b/data/exchange_rates/EUR_CZK.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Returns</t>
+          <t>Log_return</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -489,10 +489,10 @@
         <v>2000</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.034</v>
+        <v>-0.0346</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5620482880753954</v>
+        <v>-0.5532782898244656</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         <v>2001</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0891</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.04353932302813</v>
+        <v>-2.120780287095859</v>
       </c>
     </row>
     <row r="5">
@@ -532,7 +532,7 @@
         <v>-0.0049</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2203725670448331</v>
+        <v>0.239818972849476</v>
       </c>
     </row>
     <row r="6">
@@ -549,10 +549,10 @@
         <v>2003</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0231</v>
+        <v>0.0229</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9732173760952246</v>
+        <v>0.9821793736015155</v>
       </c>
     </row>
     <row r="7">
@@ -569,10 +569,10 @@
         <v>2004</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0579</v>
+        <v>-0.0597</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.204655107229122</v>
+        <v>-1.223538939424329</v>
       </c>
     </row>
     <row r="8">
@@ -589,10 +589,10 @@
         <v>2005</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0437</v>
+        <v>-0.0447</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8228552397821381</v>
+        <v>-0.8229847663566813</v>
       </c>
     </row>
     <row r="9">
@@ -609,10 +609,10 @@
         <v>2006</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0547</v>
+        <v>-0.0562</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.118615700480506</v>
+        <v>-1.130076299041878</v>
       </c>
     </row>
     <row r="10">
@@ -629,10 +629,10 @@
         <v>2007</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0358</v>
+        <v>-0.0364</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6104454543714919</v>
+        <v>-0.6013447905925833</v>
       </c>
     </row>
     <row r="11">
@@ -649,10 +649,10 @@
         <v>2008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0097</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6129273603353944</v>
+        <v>0.6270213401482017</v>
       </c>
     </row>
     <row r="12">
@@ -669,10 +669,10 @@
         <v>2009</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0163</v>
+        <v>-0.0164</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.08614281949711203</v>
+        <v>-0.06727255983572027</v>
       </c>
     </row>
     <row r="13">
@@ -689,10 +689,10 @@
         <v>2010</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0501</v>
+        <v>-0.0514</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9949340532793705</v>
+        <v>-1.00189896366023</v>
       </c>
     </row>
     <row r="14">
@@ -709,10 +709,10 @@
         <v>2011</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0218</v>
+        <v>0.0216</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9382638671035993</v>
+        <v>0.9474646786023195</v>
       </c>
     </row>
     <row r="15">
@@ -729,10 +729,10 @@
         <v>2012</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0195</v>
+        <v>-0.0196</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1721822262457282</v>
+        <v>-0.1527241167568183</v>
       </c>
     </row>
     <row r="16">
@@ -749,10 +749,10 @@
         <v>2013</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0912</v>
+        <v>0.0873</v>
       </c>
       <c r="F16" t="n">
-        <v>2.804243500964212</v>
+        <v>2.701891956638615</v>
       </c>
     </row>
     <row r="17">
@@ -769,10 +769,10 @@
         <v>2014</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0117</v>
+        <v>0.0116</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6667019895532795</v>
+        <v>0.680428563223888</v>
       </c>
     </row>
     <row r="18">
@@ -789,10 +789,10 @@
         <v>2015</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0237</v>
+        <v>-0.0239</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2851089476032869</v>
+        <v>-0.2675496463695439</v>
       </c>
     </row>
     <row r="19">
@@ -812,7 +812,7 @@
         <v>0.0003</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3601866030113344</v>
+        <v>0.3786777528462604</v>
       </c>
     </row>
     <row r="20">
@@ -829,10 +829,10 @@
         <v>2017</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0548</v>
+        <v>-0.0564</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.121304431941401</v>
+        <v>-1.135417021349446</v>
       </c>
     </row>
     <row r="21">
@@ -849,10 +849,10 @@
         <v>2018</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0067</v>
+        <v>0.0066</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5322654165085667</v>
+        <v>0.5469105055346722</v>
       </c>
     </row>
     <row r="22">
@@ -869,10 +869,10 @@
         <v>2019</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0107</v>
+        <v>-0.0108</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06442614231296626</v>
+        <v>0.0822676647762014</v>
       </c>
     </row>
     <row r="23">
@@ -889,10 +889,10 @@
         <v>2020</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0308</v>
+        <v>0.0303</v>
       </c>
       <c r="F23" t="n">
-        <v>1.180249698584082</v>
+        <v>1.179786098981555</v>
       </c>
     </row>
     <row r="24">
@@ -909,10 +909,10 @@
         <v>2021</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0512</v>
+        <v>-0.0526</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.024510099349207</v>
+        <v>-1.033943297505642</v>
       </c>
     </row>
     <row r="25">
@@ -929,10 +929,10 @@
         <v>2022</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0287</v>
+        <v>-0.0291</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4195455206479998</v>
+        <v>-0.4064084263663282</v>
       </c>
     </row>
     <row r="26">
@@ -949,10 +949,10 @@
         <v>2023</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0217</v>
+        <v>0.0215</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9355751356427051</v>
+        <v>0.9447943174485351</v>
       </c>
     </row>
     <row r="27">
@@ -969,10 +969,10 @@
         <v>2024</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0213</v>
+        <v>0.0211</v>
       </c>
       <c r="F27" t="n">
-        <v>0.924820209799128</v>
+        <v>0.9341128728333979</v>
       </c>
     </row>
     <row r="28">
@@ -992,7 +992,7 @@
         <v>-0.0037</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2526373445755641</v>
+        <v>0.2718633066948878</v>
       </c>
     </row>
   </sheetData>
